--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/IDAHO_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/IDAHO_2011.xlsx
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C94">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C544">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C580">
